--- a/output/laminas_comunales/comunal_o_ocup_a_2024_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_o_ocup_a_2024_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C99"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -384,37 +384,37 @@
         </is>
       </c>
       <c r="C2">
-        <v>40.6582604569182</v>
+        <v>55.665108579219</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C3">
-        <v>35.748496311919</v>
+        <v>55.347714201904</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C4">
-        <v>32.3199685534591</v>
+        <v>54.9060770044162</v>
       </c>
     </row>
     <row r="5">
@@ -429,127 +429,1417 @@
         </is>
       </c>
       <c r="C5">
-        <v>32.314200895282</v>
+        <v>53.3181244899473</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="C6">
-        <v>31.6001482017612</v>
+        <v>52.2126789366053</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C7">
-        <v>31.2914338360472</v>
+        <v>52.2116738413649</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="C8">
-        <v>30.5282526115859</v>
+        <v>51.9361350706552</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14107</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Paillaco</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="C9">
-        <v>29.715891592239</v>
+        <v>51.7338116261957</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14107</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Paillaco</t>
         </is>
       </c>
       <c r="C10">
-        <v>27.7636566332218</v>
+        <v>50.6251313301114</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C11">
-        <v>26.6299357208448</v>
+        <v>50.2012383900929</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C12">
-        <v>26.3361307420495</v>
+        <v>50.0569161952902</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>47.7870727870728</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>46.6937945066124</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>45.7789422075136</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>45.0982141010527</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>44.7731906218145</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>44.0103492884864</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>42.7890992403232</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>42.4957026214009</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>42.3615531508593</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>42.1957092819615</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>41.8526100307062</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
           <t>14203</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>Lago Ranco</t>
         </is>
       </c>
-      <c r="C13">
+      <c r="C24">
+        <v>41.3800963918197</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>40.6582604569182</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>40.1720455061549</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>40.1534972963544</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>39.2609758582052</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>39.1520920965242</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>38.4168987929434</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>38.3832810490177</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>37.992452712013</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>37.7929132066887</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>37.2547834843907</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>36.8721008776193</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>36.5199514064106</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>35.96980478992</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>35.748496311919</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>35.668549905838</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>34.9984422058365</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>34.3211983314372</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>33.4309202744263</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>33.2933443707182</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>33.0174828251131</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>32.8380609335134</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>32.4831460674157</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>32.3199685534591</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>32.314200895282</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>32.290963882517</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>31.8511450381679</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>31.7831307528667</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>31.6001482017612</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>31.2914338360472</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>30.7792659895738</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>30.5282526115859</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>30.1224288049884</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>29.715891592239</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>29.3102311655124</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>28.5541625696493</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>28.2371854904164</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>27.9414464023495</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>27.8722576948265</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>27.7636566332218</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>26.9662817381005</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>26.9513504780369</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>26.9143401480179</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>26.6299357208448</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>26.6001957812303</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>26.3788307328899</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>26.3361307420495</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>25.3943594646272</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>25.0365176745545</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>24.5534355018776</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C74">
         <v>24.4693153375788</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>24.3387392605464</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>23.7052977815103</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>23.5633946830266</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>23.325878991179</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>23.3132157226865</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>23.1656955365729</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>22.4648733592161</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>21.6269841269841</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>21.0685771314514</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>20.5872893348771</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>20.3973078593139</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14204</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Río Bueno</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>13.5984023238925</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>9.920906933825471</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>9.869854910019299</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>9.634884117246081</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>9.45887773417933</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>9.17880794701987</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>8.8201377219861</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>8.465091765873019</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>8.36008083689967</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>8.25272284322155</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>7.83157718682054</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>7.69430144430144</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>7.44347436758451</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>6.29734848484848</v>
       </c>
     </row>
   </sheetData>
